--- a/premise/data/additional_inventories/lci-hydrogen-turbine.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-turbine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A380463-7CE2-DD46-87F5-D3B646E5BF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1936EEB0-431A-9841-9740-1811F61F6E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{26241F67-8618-094B-AD38-E491C9570B84}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="59">
   <si>
     <t>database</t>
   </si>
@@ -206,13 +206,16 @@
     <t>electricity production, from hydrogen-fired one gigawatt gas turbine, for grid balancing</t>
   </si>
   <si>
-    <t>market for hydrogen, gaseous, low pressure</t>
-  </si>
-  <si>
-    <t>hydrogen, gaseous, low pressure</t>
-  </si>
-  <si>
     <t>H2-fed 1 GW hydrogen gas turbine. Use a CCGT dataset for infrastructure. Capacity: 1000 MW. Capacity factor: 70%. Efficiency (HHV): 95%. Yearly production: 6,004,454 MWh.</t>
+  </si>
+  <si>
+    <t>market for hydrogen, gaseous</t>
+  </si>
+  <si>
+    <t>GLO</t>
+  </si>
+  <si>
+    <t>hydrogen, gaseous</t>
   </si>
 </sst>
 </file>
@@ -586,6 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -605,7 +609,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -616,7 +621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -627,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -638,7 +643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -646,7 +651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -654,7 +659,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -665,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -676,7 +681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -687,7 +692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -695,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -721,7 +726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>B3</f>
         <v>electricity production, from hydrogen-fired one gigawatt gas turbine, for grid balancing</v>
@@ -745,7 +750,7 @@
         <v>electricity, high voltage</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -765,7 +770,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -789,7 +794,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -810,7 +815,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -830,7 +835,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -851,7 +856,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -862,7 +868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -873,7 +879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -884,7 +890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -892,7 +898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -900,7 +906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -911,7 +917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -922,7 +928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -933,7 +939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>12</v>
       </c>
@@ -941,7 +947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -967,7 +973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f>B20</f>
         <v>heat production, from hydrogen-fired one gigawatt gas turbine, for grid balancing</v>
@@ -991,7 +997,7 @@
         <v>heat</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1012,7 +1018,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -1057,7 +1063,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1078,7 +1084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -1099,7 +1105,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
@@ -1110,7 +1117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1132,15 +1139,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1148,7 +1155,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -1159,7 +1166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1170,7 +1177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -1181,7 +1188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>12</v>
       </c>
@@ -1189,7 +1196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>13</v>
       </c>
@@ -1215,7 +1222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="str">
         <f>B37</f>
         <v>heat production, from hydrogen-fired one gigawatt gas turbine</v>
@@ -1239,7 +1246,7 @@
         <v>heat</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -1262,14 +1269,14 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="3">
         <f>(1/120/0.95)*1.02</f>
         <v>8.9473684210526309E-3</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -1278,13 +1285,13 @@
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H49" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -1305,7 +1312,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -1326,7 +1333,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>43</v>
       </c>
@@ -1347,7 +1354,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
@@ -1358,7 +1366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -1380,7 +1388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -1388,7 +1396,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -1396,7 +1404,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -1407,7 +1415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -1418,7 +1426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -1429,7 +1437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>12</v>
       </c>
@@ -1437,7 +1445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>13</v>
       </c>
@@ -1463,7 +1471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="str">
         <f>B54</f>
         <v>hydrogen storage, for grid-balancing</v>
@@ -1487,7 +1495,7 @@
         <v>hydrogen, gaseous, 80 bar</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>31</v>
       </c>
@@ -1511,7 +1519,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>38</v>
       </c>
@@ -1532,7 +1540,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>26</v>
       </c>
@@ -1555,7 +1563,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>43</v>
       </c>
@@ -1577,7 +1585,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13" xr:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}"/>
+  <autoFilter ref="A1:M68" xr:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="market for hydrogen, gaseous, low pressure"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
